--- a/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-3 太陽系與星空　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上7-3 太陽系與星空　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>太陽系的中心是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>太陽</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>矮行星</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>恆星</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>八大行星由內而外第三顆是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>地球</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>人類家園</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>自行發光發熱的天體是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>遙遠恆星</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>恆星</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>如太陽</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>行星靠什麼而亮？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>木星</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>反射太陽光</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>太陽是恆星還行星？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>恆星</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>第三</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>發光</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>把星星連成的圖案是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>星座</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>辨認</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>八大行星最大的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>相距極遠</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>木星</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>類木</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>離太陽最近的行星是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>彗尾</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>水星</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>最內</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>太陽屬於恆星還行星？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>恆星</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>彗尾</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>發光</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>地球是八大行星由內往外第幾顆？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>彗尾</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>第三</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>遙遠恆星</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>地球</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-3 太陽系與星空　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上7-3 太陽系與星空　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>八大行星順序？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>恆星自行發光位置相對固定,行星反光且相對背景移動</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>較深移高中,國中認識星空為主</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>特定星座在特定季節方位出現</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>水金地火木土天海</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>由內而外</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>行星本身會發光嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>遙遠恆星</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>太陽系的能量主要來自？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>彗尾</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>太陽</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>恆星</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>彗星接近太陽會出現？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>彗尾</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>揮發</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>星座的星星實際上？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>相距極遠</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>視覺相近</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>類地行星包括？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>水金地火</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>矮行星</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>彗尾</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>岩質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>冥王星現被歸類為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>矮行星</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>非八大</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>夜空多數星星是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>遙遠恆星</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>發光</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>太陽系八大行星繞著什麼運行？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>太陽</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>繞日</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>太陽系能量的主要來源是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>恆星</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>太陽</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>恆星</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-3 太陽系與星空　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上7-3 太陽系與星空　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何行星不發光卻能被看見？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>反射太陽光</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>星座</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>水金地火</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>如何區分天上的恆星與行星？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>恆星自行發光位置相對固定,行星反光且相對背景移動</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>提供光熱維持生命與氣候</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>類地岩質較小、類木氣態巨大</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>特定星座在特定季節方位出現</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>區分</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>星座為何能用來辨方位季節？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>水金地火木土天海</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>特定星座在特定季節方位出現</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>衛星小行星彗星矮行星</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>只是視線方向相近深度不同</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>太陽系除行星外還有哪些天體？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>衛星小行星彗星矮行星</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>提供光熱維持生命與氣候</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>衛星小行星彗星等</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>恆星自行發光位置相對固定,行星反光且相對背景移動</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>類地與類木行星主要差別？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>衛星小行星彗星等</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>衛星小行星彗星矮行星</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>類地岩質較小、類木氣態巨大</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>只是視線方向相近深度不同</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>為何星座中的星實際相距遙遠？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>只是視線方向相近深度不同</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>衛星小行星彗星等</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>提供光熱維持生命與氣候</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>恆星自行發光位置相對固定,行星反光且相對背景移動</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>視覺</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>太陽作為恆星對地球的重要性？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>提供光熱維持生命與氣候</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>只是視線方向相近深度不同</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>恆星自行發光位置相對固定,行星反光且相對背景移動</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>類地岩質較小、類木氣態巨大</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>重要</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱刪除恆星周日運動細節？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>特定星座在特定季節方位出現</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>水金地火木土天海</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>提供光熱維持生命與氣候</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>較深移高中,國中認識星空為主</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>如何分辨夜空中的恆星與行星？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>恆星自行發光、行星反光且相對移動</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>衛星小行星彗星矮行星</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>提供光熱維持生命與氣候</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>類地岩質較小、類木氣態巨大</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>區分</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>太陽系除八大行星外還有哪些天體？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>水金地火木土天海</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>只是視線方向相近深度不同</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>衛星小行星彗星等</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>特定星座在特定季節方位出現</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>恆星</t>
+          <t>恆星：太陽是太陽系質量最大的天體，各行星都受太陽重力吸引繞著它公轉，是太陽系的中心</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>人類家園</t>
+          <t>人類家園：依照距離太陽由近到遠排列，地球是第三顆行星，也是目前已知唯一有生命存在的行星</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>如太陽</t>
+          <t>如太陽：能夠自己進行核融合反應、持續發光發熱的天體稱為恆星，太陽就是離我們最近的恆星</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：行星本身不會發光，我們能看到行星是因為它反射了太陽的光線</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>發光</t>
+          <t>發光：太陽能自行進行核融合反應持續發光發熱，屬於恆星，不是繞著別的星體運行的行星</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>辨認</t>
+          <t>辨認：把夜空中特定幾顆星星依照排列位置連成圖案並命名，方便辨認與定位，這樣的圖案稱為星座</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>類木</t>
+          <t>類木：木星是太陽系八大行星中體積和質量最大的一顆，屬於氣態的類木行星</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>最內</t>
+          <t>最內：水星是距離太陽最近的行星，公轉軌道在八大行星中最靠內側</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>發光</t>
+          <t>發光：太陽自己能持續進行核融合反應發光發熱,屬於恆星,不是繞著別的星體轉的行星</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>地球：太陽系八大行星由內往外依序是水星、金星、地球、火星…,地球排在第三顆</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>由內而外</t>
+          <t>由內而外：依照距離太陽由近到遠排列，八大行星依序是水星、金星、地球、火星、木星、土星、天王星、海王星</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：行星本身不會自行發光，我們看到的行星光亮是它反射太陽光的緣故</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>恆星</t>
+          <t>恆星：太陽系中絕大部分的光和熱能量，都是由太陽這顆恆星持續進行核融合反應所提供的</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>揮發</t>
+          <t>揮發：彗星接近太陽時，表面的冰質受熱揮發成氣體和塵埃，被太陽風吹向後方，形成長長的彗尾</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>視覺相近</t>
+          <t>視覺相近：組成同一星座的星星，實際上彼此之間的距離往往非常遙遠，只是從地球上看去、在同一個視線方向上顯得相近而已</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>岩質</t>
+          <t>岩質：水星、金星、地球、火星這四顆行星主要由岩石組成、體積較小，合稱類地行星</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>非八大</t>
+          <t>非八大：冥王星因為軌道特性和體積不符合行星的最新定義標準，現在被重新歸類為矮行星，不再屬於太陽系八大行星之一</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發光</t>
+          <t>發光：夜空中我們看到閃爍的星星，絕大多數都是距離極為遙遠、能自行發光發熱的恆星</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>繞日</t>
+          <t>繞日：太陽系中的八大行星都受到太陽的重力吸引,環繞著太陽公轉運行</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>恆星</t>
+          <t>恆星：太陽系中絕大部分的光和熱能量,都是由太陽這顆恆星持續核融合反應所提供的</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：行星本身不像恆星那樣能自行發光發熱，但能反射照射到它表面的太陽光，這些反射光傳到我們眼睛，所以行星才能被看見</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>區分</t>
+          <t>區分：恆星本身會發光且相對於其他星星位置固定不太移動(閃爍較明顯)；行星本身不發光、靠反射太陽光才看得見，而且相對於背景恆星會緩慢移動位置，可用這些特徵來分辨</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：由於地球公轉，不同季節夜晚面向的星空背景不同，特定星座固定會在特定季節、特定方位的天空中出現，因此可以利用星座來輔助辨認方位和季節</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：太陽系除了八大行星，還包含繞行星運轉的衛星、散布在小行星帶的小行星、軌道細長的彗星、以及像冥王星這樣的矮行星等各種天體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>分類：類地行星(水金地火)主要由岩石構成、體積較小、密度較大；類木行星(木土天海)則主要由氣體構成、體積龐大、密度較小，兩類行星的組成和大小明顯不同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>視覺</t>
+          <t>視覺：組成同一星座的星星只是從地球望去、剛好落在相近的視線方向上，但它們與地球的實際距離(深度)可能差異極大，彼此之間的真實距離也非常遙遠，只是看起來像連成一片而已</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>重要</t>
+          <t>重要：太陽持續提供地球光和熱能量，不僅是地球生物賴以維生的能量來源，也主導了地球的氣候系統，對地球至關重要</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：恆星周日運動牽涉較複雜的天球座標與地球自轉細節，依課綱安排移到高中階段深入學習，國中階段的重點放在初步認識星空與太陽系組成即可</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>區分</t>
+          <t>區分：恆星本身會發光且位置相對固定(閃爍較明顯);行星本身不發光、靠反射太陽光才看得見,而且相對於背景恆星會緩慢移動位置,可用這些特徵來分辨</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：太陽系除了八大行星,還包含繞行星運轉的衛星、散布在小行星帶的小行星、以及軌道細長的彗星等各種天體</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>矮行星</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>相距極遠</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>水金地火</t>
+          <t>星座</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>反射太陽光</t>
+          <t>相距極遠</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>彗尾</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>遙遠恆星</t>
+          <t>木星</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>木星</t>
+          <t>星座</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>太陽</t>
+          <t>恆星</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>星座</t>
+          <t>水金地火</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>星座</t>
+          <t>第三</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>第三</t>
+          <t>水金地火</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>反射太陽光</t>
+          <t>相距極遠</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>太陽</t>
+          <t>第三</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>彗尾</t>
+          <t>星座</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>反射太陽光</t>
+          <t>水星</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>彗尾</t>
+          <t>木星</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>恆星</t>
+          <t>第三</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>太陽</t>
+          <t>彗尾</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>木星</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>相距極遠</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>第三</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>木星</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>星座</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>水金地火</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>第三</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>水金地火</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>太陽</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
